--- a/Unpack_and_Explain_Tracker.xlsx
+++ b/Unpack_and_Explain_Tracker.xlsx
@@ -2400,7 +2400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="46" min="1" max="1"/>
@@ -2416,14 +2416,14 @@
     <row r="1" ht="19.7" customHeight="1" s="47">
       <c r="A1" s="48" t="inlineStr">
         <is>
-          <t>Week 1 Scripts (30-40 sec each)</t>
+          <t>Week 1 Scripts (35-52 sec each)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="47">
       <c r="A2" s="49" t="inlineStr">
         <is>
-          <t>Template: Hook, Setup, Mechanism, Payoff, CTA. Target 90-110 spoken words per reel. Figures marked 'verify' need a source check before posting.</t>
+          <t>Template: Question, Hook, Setup, Mechanism, Payoff, Congrats, CTA. Question asks the viewer about the topic and ends with '?'. Congrats starts with 'Congrats,' (comma, not '!'). CTA is always 'Follow Unpack and Explain for how things actually work.' Target 100-130 spoken words per reel. Figures marked 'verify' need a source check before posting.</t>
         </is>
       </c>
     </row>
@@ -2505,22 +2505,22 @@
       </c>
       <c r="C7" s="66" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="D7" s="65" t="inlineStr">
         <is>
-          <t>0-3s</t>
+          <t>0-4s</t>
         </is>
       </c>
       <c r="E7" s="52" t="inlineStr">
         <is>
-          <t>You tap your card, and it's approved in two seconds. In that time, up to five companies talk about you.</t>
+          <t>Do you know what really happens when you tap your card?</t>
         </is>
       </c>
       <c r="F7" s="52" t="inlineStr">
         <is>
-          <t>Card taps a terminal; five dots light up one by one.</t>
+          <t>Question card (template).</t>
         </is>
       </c>
       <c r="G7" s="65">
@@ -2545,22 +2545,22 @@
       </c>
       <c r="C8" s="66" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="D8" s="65" t="inlineStr">
         <is>
-          <t>3-8s</t>
+          <t>4-12s</t>
         </is>
       </c>
       <c r="E8" s="52" t="inlineStr">
         <is>
-          <t>Your card doesn't hold your money. It holds a number that points to your bank.</t>
+          <t>You tap your card, and it's approved in two seconds. In that time, up to five companies talk about you.</t>
         </is>
       </c>
       <c r="F8" s="52" t="inlineStr">
         <is>
-          <t>Card morphs into a number, then an arrow to a bank icon.</t>
+          <t>Card taps a terminal; five dots light up one by one.</t>
         </is>
       </c>
       <c r="G8" s="65">
@@ -2572,7 +2572,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="75.75" customHeight="1" s="47">
+    <row r="9" ht="33.75" customHeight="1" s="47">
       <c r="A9" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -2585,22 +2585,22 @@
       </c>
       <c r="C9" s="66" t="inlineStr">
         <is>
-          <t>Mechanism</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="D9" s="65" t="inlineStr">
         <is>
-          <t>8-28s</t>
+          <t>12-18s</t>
         </is>
       </c>
       <c r="E9" s="52" t="inlineStr">
         <is>
-          <t>The terminal sends your request to the shop's bank. That bank passes it to the card network. The network finds your bank. Your bank checks your balance and fraud signals, then says yes or no. The answer races back.</t>
+          <t>Your card doesn't hold your money. It holds a number that points to your bank.</t>
         </is>
       </c>
       <c r="F9" s="52" t="inlineStr">
         <is>
-          <t>Left-to-right chain: Terminal &gt; Shop's bank &gt; Card network &gt; Your bank. A glowing packet travels forward, then returns with a green tick. Step numbers 1-4 pop in.</t>
+          <t>Card morphs into a number, then an arrow to a bank icon.</t>
         </is>
       </c>
       <c r="G9" s="65">
@@ -2612,7 +2612,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1" s="47">
+    <row r="10" ht="33.75" customHeight="1" s="47">
       <c r="A10" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C10" s="66" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>Mechanism</t>
         </is>
       </c>
       <c r="D10" s="65" t="inlineStr">
         <is>
-          <t>28-35s</t>
+          <t>18-34s</t>
         </is>
       </c>
       <c r="E10" s="52" t="inlineStr">
         <is>
-          <t>But no money has moved yet. Those two seconds only bought a promise. Settlement, the real transfer, comes a day or two later.</t>
+          <t>The terminal sends your request to the shop's bank. That bank passes it to the card network. The network finds your bank. Your bank checks your balance and fraud signals, then says yes or no. The answer races back.</t>
         </is>
       </c>
       <c r="F10" s="52" t="inlineStr">
         <is>
-          <t>Chain greys out; a calendar flips forward.</t>
+          <t>Left-to-right chain: Terminal &gt; Shop's bank &gt; Card network &gt; Your bank. A glowing packet travels forward, then returns with a green tick. Step numbers 1-4 pop in.</t>
         </is>
       </c>
       <c r="G10" s="65">
@@ -2665,22 +2665,22 @@
       </c>
       <c r="C11" s="66" t="inlineStr">
         <is>
-          <t>CTA</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="D11" s="65" t="inlineStr">
         <is>
-          <t>35-38s</t>
+          <t>34-43s</t>
         </is>
       </c>
       <c r="E11" s="52" t="inlineStr">
         <is>
-          <t>Follow Unpack and Explain for how things actually work.</t>
+          <t>But no money has moved yet. Those two seconds only bought a promise. Settlement, the real transfer, comes a day or two later.</t>
         </is>
       </c>
       <c r="F11" s="52" t="inlineStr">
         <is>
-          <t>Logo + tagline card.</t>
+          <t>Chain greys out; a calendar flips forward.</t>
         </is>
       </c>
       <c r="G11" s="65">
@@ -2692,170 +2692,170 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="47">
-      <c r="A12" s="67" t="n"/>
-      <c r="B12" s="67" t="n"/>
-      <c r="C12" s="67" t="inlineStr">
+    <row r="12" ht="33.75" customHeight="1" s="47">
+      <c r="A12" s="65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="65" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C12" s="66" t="inlineStr">
+        <is>
+          <t>Congrats</t>
+        </is>
+      </c>
+      <c r="D12" s="65" t="inlineStr">
+        <is>
+          <t>43-47s</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="inlineStr">
+        <is>
+          <t>Congrats, you just learned how a card payment works.</t>
+        </is>
+      </c>
+      <c r="F12" s="52" t="inlineStr">
+        <is>
+          <t>Congrats card: teal check + chime (template).</t>
+        </is>
+      </c>
+      <c r="G12" s="65">
+        <f>LEN(TRIM(E12))-LEN(SUBSTITUTE(TRIM(E12)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H12" s="58">
+        <f>G12/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="33.75" customHeight="1" s="47">
+      <c r="A13" s="65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" s="65" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C13" s="66" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+      <c r="D13" s="65" t="inlineStr">
+        <is>
+          <t>47-50s</t>
+        </is>
+      </c>
+      <c r="E13" s="52" t="inlineStr">
+        <is>
+          <t>Follow Unpack and Explain for how things actually work.</t>
+        </is>
+      </c>
+      <c r="F13" s="52" t="inlineStr">
+        <is>
+          <t>Logo + tagline card.</t>
+        </is>
+      </c>
+      <c r="G13" s="65">
+        <f>LEN(TRIM(E13))-LEN(SUBSTITUTE(TRIM(E13)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H13" s="58">
+        <f>G13/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="33.75" customHeight="1" s="47">
+      <c r="A14" s="67" t="n"/>
+      <c r="B14" s="67" t="n"/>
+      <c r="C14" s="67" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D12" s="67" t="n"/>
-      <c r="E12" s="68">
-        <f>IF(AND(G12&gt;=90,G12&lt;=110),"Within the 90-110 word target","Outside the 90-110 word target")</f>
-        <v/>
-      </c>
-      <c r="F12" s="67" t="n"/>
-      <c r="G12" s="67">
-        <f>SUM(G7:G11)</f>
-        <v/>
-      </c>
-      <c r="H12" s="69">
-        <f>SUM(H7:H11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" s="47">
-      <c r="C13" s="70" t="inlineStr">
+      <c r="D14" s="67" t="n"/>
+      <c r="E14" s="68">
+        <f>IF(AND(G14&gt;=100,G14&lt;=130),"Within the 100-130 word target","Outside the 100-130 word target")</f>
+        <v/>
+      </c>
+      <c r="F14" s="67" t="n"/>
+      <c r="G14" s="67">
+        <f>SUM(G7:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="69">
+        <f>SUM(H7:H13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="33.75" customHeight="1" s="47">
+      <c r="C15" s="70" t="inlineStr">
         <is>
           <t>Sources / verify</t>
         </is>
       </c>
-      <c r="D13" s="71" t="inlineStr">
+      <c r="D15" s="71" t="inlineStr">
         <is>
           <t>Verify: settlement timing varies by country and card network. Cite the source on screen.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="33.75" customHeight="1" s="47">
-      <c r="C14" s="70" t="inlineStr">
+    <row r="16" ht="33.75" customHeight="1" s="47">
+      <c r="C16" s="70" t="inlineStr">
         <is>
           <t>Caption + hashtags</t>
         </is>
       </c>
-      <c r="D14" s="72" t="inlineStr">
+      <c r="D16" s="71" t="inlineStr">
         <is>
           <t>Tapping your card feels instant, but there's a whole relay behind it. Save this for the next time someone asks how card payments work.  #howitworks #payments #fintech #explained</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16" ht="24" customHeight="1" s="47">
-      <c r="A16" s="64" t="inlineStr">
+    <row r="17" ht="33.75" customHeight="1" s="47"/>
+    <row r="18" ht="24" customHeight="1" s="47">
+      <c r="A18" s="64" t="inlineStr">
         <is>
           <t>Post 2  |  E  |  How GPS finds you</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="33.75" customHeight="1" s="47">
-      <c r="A17" s="65" t="inlineStr">
+    <row r="19" ht="33.75" customHeight="1" s="47">
+      <c r="A19" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B17" s="65" t="inlineStr">
+      <c r="B19" s="65" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C17" s="66" t="inlineStr">
-        <is>
-          <t>Hook</t>
-        </is>
-      </c>
-      <c r="D17" s="65" t="inlineStr">
+      <c r="C19" s="66" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="D19" s="65" t="inlineStr">
         <is>
           <t>0-3s</t>
         </is>
       </c>
-      <c r="E17" s="52" t="inlineStr">
-        <is>
-          <t>GPS doesn't track you. Your phone just listens.</t>
-        </is>
-      </c>
-      <c r="F17" s="52" t="inlineStr">
-        <is>
-          <t>Phone icon with ears/sound waves; satellite beams arrive, nothing goes back.</t>
-        </is>
-      </c>
-      <c r="G17" s="65">
-        <f>LEN(TRIM(E17))-LEN(SUBSTITUTE(TRIM(E17)," ",""))+1</f>
-        <v/>
-      </c>
-      <c r="H17" s="58">
-        <f>G17/$D$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="33.75" customHeight="1" s="47">
-      <c r="A18" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B18" s="65" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C18" s="66" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="D18" s="65" t="inlineStr">
-        <is>
-          <t>3-8s</t>
-        </is>
-      </c>
-      <c r="E18" s="52" t="inlineStr">
-        <is>
-          <t>About thirty satellites circle the Earth, and all they do is broadcast the time.</t>
-        </is>
-      </c>
-      <c r="F18" s="52" t="inlineStr">
-        <is>
-          <t>Orbit animation, satellites emitting expanding rings.</t>
-        </is>
-      </c>
-      <c r="G18" s="65">
-        <f>LEN(TRIM(E18))-LEN(SUBSTITUTE(TRIM(E18)," ",""))+1</f>
-        <v/>
-      </c>
-      <c r="H18" s="58">
-        <f>G18/$D$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="75.75" customHeight="1" s="47">
-      <c r="A19" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B19" s="65" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C19" s="66" t="inlineStr">
-        <is>
-          <t>Mechanism</t>
-        </is>
-      </c>
-      <c r="D19" s="65" t="inlineStr">
-        <is>
-          <t>8-28s</t>
-        </is>
-      </c>
       <c r="E19" s="52" t="inlineStr">
         <is>
-          <t>Each signal carries the satellite's position and the exact moment it was sent. Your phone measures how late each signal arrives. Delay times the speed of light gives distance. Three distances pin down your position. A fourth fixes your phone's clock.</t>
+          <t>Do you know how GPS actually finds you?</t>
         </is>
       </c>
       <c r="F19" s="52" t="inlineStr">
         <is>
-          <t>Circles from 3 satellites overlap at one point; a 4th circle snaps in and a small clock icon corrects itself.</t>
+          <t>Question card (template).</t>
         </is>
       </c>
       <c r="G19" s="65">
@@ -2867,7 +2867,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="61.5" customHeight="1" s="47">
+    <row r="20" ht="33.75" customHeight="1" s="47">
       <c r="A20" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -2880,22 +2880,22 @@
       </c>
       <c r="C20" s="66" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="D20" s="65" t="inlineStr">
         <is>
-          <t>28-35s</t>
+          <t>3-6s</t>
         </is>
       </c>
       <c r="E20" s="52" t="inlineStr">
         <is>
-          <t>Your phone never sends anything back, so GPS works with no internet. And the satellites' clocks are corrected for relativity. Skip that, and you'd drift by several kilometers every day.</t>
+          <t>GPS doesn't track you. Your phone just listens.</t>
         </is>
       </c>
       <c r="F20" s="52" t="inlineStr">
         <is>
-          <t>Phone shows airplane mode and still has a location pin. Clock with a tiny correction arrow.</t>
+          <t>Phone icon with ears/sound waves; satellite beams arrive, nothing goes back.</t>
         </is>
       </c>
       <c r="G20" s="65">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>CTA</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="D21" s="65" t="inlineStr">
         <is>
-          <t>35-38s</t>
+          <t>6-12s</t>
         </is>
       </c>
       <c r="E21" s="52" t="inlineStr">
         <is>
-          <t>Follow Unpack and Explain for how things actually work.</t>
+          <t>About thirty GPS satellites orbit Earth, broadcasting precise timing signals and their positions.</t>
         </is>
       </c>
       <c r="F21" s="52" t="inlineStr">
         <is>
-          <t>Logo + tagline card.</t>
+          <t>Orbit animation, satellites emitting expanding rings.</t>
         </is>
       </c>
       <c r="G21" s="65">
@@ -2947,219 +2947,219 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="47">
-      <c r="A22" s="67" t="n"/>
-      <c r="B22" s="67" t="n"/>
-      <c r="C22" s="67" t="inlineStr">
+    <row r="22" ht="33.75" customHeight="1" s="47">
+      <c r="A22" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" s="65" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C22" s="66" t="inlineStr">
+        <is>
+          <t>Mechanism</t>
+        </is>
+      </c>
+      <c r="D22" s="65" t="inlineStr">
+        <is>
+          <t>12-28s</t>
+        </is>
+      </c>
+      <c r="E22" s="52" t="inlineStr">
+        <is>
+          <t>Each signal carries the satellite's position and the exact moment it was sent. Your phone measures how late each signal arrives. Delay times the speed of light gives distance. Three satellites can illustrate how your position is calculated. A fourth lets your phone solve for its own clock error, too.</t>
+        </is>
+      </c>
+      <c r="F22" s="52" t="inlineStr">
+        <is>
+          <t>Circles from 3 satellites overlap at one point; a 4th circle snaps in and a small clock icon corrects itself.</t>
+        </is>
+      </c>
+      <c r="G22" s="65">
+        <f>LEN(TRIM(E22))-LEN(SUBSTITUTE(TRIM(E22)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H22" s="58">
+        <f>G22/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="33.75" customHeight="1" s="47">
+      <c r="A23" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="65" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C23" s="66" t="inlineStr">
+        <is>
+          <t>Payoff</t>
+        </is>
+      </c>
+      <c r="D23" s="65" t="inlineStr">
+        <is>
+          <t>28-40s</t>
+        </is>
+      </c>
+      <c r="E23" s="52" t="inlineStr">
+        <is>
+          <t>Your phone never sends anything back, so GPS works with no internet. And the satellites' clocks are corrected for relativity. Skip that, and you'd drift by several kilometers every day.</t>
+        </is>
+      </c>
+      <c r="F23" s="52" t="inlineStr">
+        <is>
+          <t>Phone shows airplane mode and still has a location pin. Clock with a tiny correction arrow.</t>
+        </is>
+      </c>
+      <c r="G23" s="65">
+        <f>LEN(TRIM(E23))-LEN(SUBSTITUTE(TRIM(E23)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H23" s="58">
+        <f>G23/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="33.75" customHeight="1" s="47">
+      <c r="A24" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B24" s="65" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C24" s="66" t="inlineStr">
+        <is>
+          <t>Congrats</t>
+        </is>
+      </c>
+      <c r="D24" s="65" t="inlineStr">
+        <is>
+          <t>40-44s</t>
+        </is>
+      </c>
+      <c r="E24" s="52" t="inlineStr">
+        <is>
+          <t>Congrats, you just learned how GPS finds you.</t>
+        </is>
+      </c>
+      <c r="F24" s="52" t="inlineStr">
+        <is>
+          <t>Congrats card: teal check + chime (template).</t>
+        </is>
+      </c>
+      <c r="G24" s="65">
+        <f>LEN(TRIM(E24))-LEN(SUBSTITUTE(TRIM(E24)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H24" s="58">
+        <f>G24/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="33.75" customHeight="1" s="47">
+      <c r="A25" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" s="65" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C25" s="66" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+      <c r="D25" s="65" t="inlineStr">
+        <is>
+          <t>44-47s</t>
+        </is>
+      </c>
+      <c r="E25" s="52" t="inlineStr">
+        <is>
+          <t>Follow Unpack and Explain for how things actually work.</t>
+        </is>
+      </c>
+      <c r="F25" s="52" t="inlineStr">
+        <is>
+          <t>Logo + tagline card.</t>
+        </is>
+      </c>
+      <c r="G25" s="65">
+        <f>LEN(TRIM(E25))-LEN(SUBSTITUTE(TRIM(E25)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H25" s="58">
+        <f>G25/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" s="47">
+      <c r="A26" s="67" t="n"/>
+      <c r="B26" s="67" t="n"/>
+      <c r="C26" s="67" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D22" s="67" t="n"/>
-      <c r="E22" s="68">
-        <f>IF(AND(G22&gt;=90,G22&lt;=110),"Within the 90-110 word target","Outside the 90-110 word target")</f>
-        <v/>
-      </c>
-      <c r="F22" s="67" t="n"/>
-      <c r="G22" s="67">
-        <f>SUM(G17:G21)</f>
-        <v/>
-      </c>
-      <c r="H22" s="69">
-        <f>SUM(H17:H21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="33.75" customHeight="1" s="47">
-      <c r="C23" s="70" t="inlineStr">
+      <c r="D26" s="67" t="n"/>
+      <c r="E26" s="68">
+        <f>IF(AND(G26&gt;=100,G26&lt;=130),"Within the 100-130 word target","Outside the 100-130 word target")</f>
+        <v/>
+      </c>
+      <c r="F26" s="67" t="n"/>
+      <c r="G26" s="67">
+        <f>SUM(G19:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="69">
+        <f>SUM(H19:H25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="33.75" customHeight="1" s="47">
+      <c r="C27" s="70" t="inlineStr">
         <is>
           <t>Sources / verify</t>
         </is>
       </c>
-      <c r="D23" s="71" t="inlineStr">
+      <c r="D27" s="71" t="inlineStr">
         <is>
           <t>Verify: satellite count (about 30 operational), altitude, and the relativity drift figure (commonly cited around 10 km/day). Source: GPS.gov.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="33.75" customHeight="1" s="47">
-      <c r="C24" s="70" t="inlineStr">
+    <row r="28" ht="33.75" customHeight="1" s="47">
+      <c r="C28" s="70" t="inlineStr">
         <is>
           <t>Caption + hashtags</t>
         </is>
       </c>
-      <c r="D24" s="72" t="inlineStr">
+      <c r="D28" s="71" t="inlineStr">
         <is>
           <t>Your phone doesn't talk to GPS satellites. It only listens. Save this for the next time you hear 'GPS is tracking me'.  #GPS #howitworks #technology #explained</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26" ht="24" customHeight="1" s="47">
-      <c r="A26" s="73" t="inlineStr">
+    <row r="29" ht="61.5" customHeight="1" s="47"/>
+    <row r="30" ht="24" customHeight="1" s="47">
+      <c r="A30" s="64" t="inlineStr">
         <is>
           <t>Post 3  |  F  |  How a jet engine works + Gimli Glider</t>
         </is>
-      </c>
-    </row>
-    <row r="27" ht="33.75" customHeight="1" s="47">
-      <c r="A27" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B27" s="65" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C27" s="66" t="inlineStr">
-        <is>
-          <t>Hook</t>
-        </is>
-      </c>
-      <c r="D27" s="65" t="inlineStr">
-        <is>
-          <t>0-3s</t>
-        </is>
-      </c>
-      <c r="E27" s="52" t="inlineStr">
-        <is>
-          <t>In 1983, a passenger jet lost both engines at 41,000 feet. Everyone survived. Here's why.</t>
-        </is>
-      </c>
-      <c r="F27" s="52" t="inlineStr">
-        <is>
-          <t>Plane silhouette high over clouds; engine glow cuts out.</t>
-        </is>
-      </c>
-      <c r="G27" s="65">
-        <f>LEN(TRIM(E27))-LEN(SUBSTITUTE(TRIM(E27)," ",""))+1</f>
-        <v/>
-      </c>
-      <c r="H27" s="58">
-        <f>G27/$D$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="33.75" customHeight="1" s="47">
-      <c r="A28" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B28" s="65" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C28" s="66" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="D28" s="65" t="inlineStr">
-        <is>
-          <t>3-8s</t>
-        </is>
-      </c>
-      <c r="E28" s="52" t="inlineStr">
-        <is>
-          <t>A jet engine is a machine that burns fuel without stopping.</t>
-        </is>
-      </c>
-      <c r="F28" s="52" t="inlineStr">
-        <is>
-          <t>Cutaway of a turbofan engine.</t>
-        </is>
-      </c>
-      <c r="G28" s="65">
-        <f>LEN(TRIM(E28))-LEN(SUBSTITUTE(TRIM(E28)," ",""))+1</f>
-        <v/>
-      </c>
-      <c r="H28" s="58">
-        <f>G28/$D$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="61.5" customHeight="1" s="47">
-      <c r="A29" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B29" s="65" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C29" s="66" t="inlineStr">
-        <is>
-          <t>Mechanism</t>
-        </is>
-      </c>
-      <c r="D29" s="65" t="inlineStr">
-        <is>
-          <t>8-28s</t>
-        </is>
-      </c>
-      <c r="E29" s="52" t="inlineStr">
-        <is>
-          <t>Suck: a fan pulls in air. Squeeze: a compressor packs it tight. Bang: fuel burns in the middle. Blow: hot gas spins a turbine, then blasts out the back and pushes the plane forward.</t>
-        </is>
-      </c>
-      <c r="F29" s="52" t="inlineStr">
-        <is>
-          <t>Four labeled stages light up in order along the engine cutaway (Suck, Squeeze, Bang, Blow).</t>
-        </is>
-      </c>
-      <c r="G29" s="65">
-        <f>LEN(TRIM(E29))-LEN(SUBSTITUTE(TRIM(E29)," ",""))+1</f>
-        <v/>
-      </c>
-      <c r="H29" s="58">
-        <f>G29/$D$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="75.75" customHeight="1" s="47">
-      <c r="A30" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B30" s="65" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C30" s="66" t="inlineStr">
-        <is>
-          <t>Payoff</t>
-        </is>
-      </c>
-      <c r="D30" s="65" t="inlineStr">
-        <is>
-          <t>28-35s</t>
-        </is>
-      </c>
-      <c r="E30" s="52" t="inlineStr">
-        <is>
-          <t>Air Canada Flight 143 ran dry after a pounds-versus-kilograms mix-up in the fuel calculation. The plane got less than half the fuel it needed. The pilots glided to an airfield in Gimli, Canada, and landed safely.</t>
-        </is>
-      </c>
-      <c r="F30" s="52" t="inlineStr">
-        <is>
-          <t>Fuel gauge drains; unit labels lb and kg swap; glide path line arcs down to a runway.</t>
-        </is>
-      </c>
-      <c r="G30" s="65">
-        <f>LEN(TRIM(E30))-LEN(SUBSTITUTE(TRIM(E30)," ",""))+1</f>
-        <v/>
-      </c>
-      <c r="H30" s="58">
-        <f>G30/$D$3</f>
-        <v/>
       </c>
     </row>
     <row r="31" ht="33.75" customHeight="1" s="47">
@@ -3175,22 +3175,22 @@
       </c>
       <c r="C31" s="66" t="inlineStr">
         <is>
-          <t>CTA</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="D31" s="65" t="inlineStr">
         <is>
-          <t>35-38s</t>
+          <t>0-4s</t>
         </is>
       </c>
       <c r="E31" s="52" t="inlineStr">
         <is>
-          <t>Follow Unpack and Explain for how things actually work.</t>
+          <t>Do you know how a jet engine actually works?</t>
         </is>
       </c>
       <c r="F31" s="52" t="inlineStr">
         <is>
-          <t>Logo + tagline card.</t>
+          <t>Question card (template).</t>
         </is>
       </c>
       <c r="G31" s="65">
@@ -3202,90 +3202,235 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="47">
-      <c r="A32" s="67" t="n"/>
-      <c r="B32" s="67" t="n"/>
-      <c r="C32" s="67" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D32" s="67" t="n"/>
-      <c r="E32" s="68">
-        <f>IF(AND(G32&gt;=90,G32&lt;=110),"Within the 90-110 word target","Outside the 90-110 word target")</f>
-        <v/>
-      </c>
-      <c r="F32" s="67" t="n"/>
-      <c r="G32" s="67">
-        <f>SUM(G27:G31)</f>
-        <v/>
-      </c>
-      <c r="H32" s="69">
-        <f>SUM(H27:H31)</f>
+    <row r="32" ht="33.75" customHeight="1" s="47">
+      <c r="A32" s="65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="65" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C32" s="66" t="inlineStr">
+        <is>
+          <t>Hook</t>
+        </is>
+      </c>
+      <c r="D32" s="65" t="inlineStr">
+        <is>
+          <t>4-10s</t>
+        </is>
+      </c>
+      <c r="E32" s="52" t="inlineStr">
+        <is>
+          <t>In 1983, a passenger jet lost both engines at 41,000 feet. Everyone survived. Here's why.</t>
+        </is>
+      </c>
+      <c r="F32" s="52" t="inlineStr">
+        <is>
+          <t>Plane silhouette high over clouds; engine glow cuts out.</t>
+        </is>
+      </c>
+      <c r="G32" s="65">
+        <f>LEN(TRIM(E32))-LEN(SUBSTITUTE(TRIM(E32)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H32" s="58">
+        <f>G32/$D$3</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="33.75" customHeight="1" s="47">
-      <c r="C33" s="70" t="inlineStr">
-        <is>
-          <t>Sources / verify</t>
-        </is>
-      </c>
-      <c r="D33" s="71" t="inlineStr">
-        <is>
-          <t>Verify: altitude, fuel amounts, and that nobody was killed. Source: Canadian investigation report on Air Canada Flight 143. Keep the tone factual and credit the crew's skill.</t>
-        </is>
+      <c r="A33" s="65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B33" s="65" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C33" s="66" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="D33" s="65" t="inlineStr">
+        <is>
+          <t>10-14s</t>
+        </is>
+      </c>
+      <c r="E33" s="52" t="inlineStr">
+        <is>
+          <t>A jet engine is a machine that burns fuel without stopping.</t>
+        </is>
+      </c>
+      <c r="F33" s="52" t="inlineStr">
+        <is>
+          <t>Cutaway of a turbofan engine.</t>
+        </is>
+      </c>
+      <c r="G33" s="65">
+        <f>LEN(TRIM(E33))-LEN(SUBSTITUTE(TRIM(E33)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H33" s="58">
+        <f>G33/$D$3</f>
+        <v/>
       </c>
     </row>
     <row r="34" ht="33.75" customHeight="1" s="47">
-      <c r="C34" s="70" t="inlineStr">
-        <is>
-          <t>Caption + hashtags</t>
-        </is>
-      </c>
-      <c r="D34" s="72" t="inlineStr">
-        <is>
-          <t>Both engines stopped at 41,000 feet and the crew still landed the plane. Here's how a jet engine works, and what went wrong. Save for later.  #aviation #engineering #howitworks #explained</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36" ht="24" customHeight="1" s="47">
-      <c r="A36" s="64" t="inlineStr">
-        <is>
-          <t>Post 4  |  Q  |  Myth: planes fly because air pushes up from below</t>
-        </is>
+      <c r="A34" s="65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B34" s="65" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C34" s="66" t="inlineStr">
+        <is>
+          <t>Mechanism</t>
+        </is>
+      </c>
+      <c r="D34" s="65" t="inlineStr">
+        <is>
+          <t>14-28s</t>
+        </is>
+      </c>
+      <c r="E34" s="52" t="inlineStr">
+        <is>
+          <t>Suck: a fan pulls in air. Squeeze: a compressor packs it tight. Bang: fuel burns in the middle. Blow: hot gas spins a turbine, then blasts out the back and pushes the plane forward.</t>
+        </is>
+      </c>
+      <c r="F34" s="52" t="inlineStr">
+        <is>
+          <t>Four labeled stages light up in order along the engine cutaway (Suck, Squeeze, Bang, Blow).</t>
+        </is>
+      </c>
+      <c r="G34" s="65">
+        <f>LEN(TRIM(E34))-LEN(SUBSTITUTE(TRIM(E34)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H34" s="58">
+        <f>G34/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="33.75" customHeight="1" s="47">
+      <c r="A35" s="65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="65" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C35" s="66" t="inlineStr">
+        <is>
+          <t>Payoff</t>
+        </is>
+      </c>
+      <c r="D35" s="65" t="inlineStr">
+        <is>
+          <t>28-42s</t>
+        </is>
+      </c>
+      <c r="E35" s="52" t="inlineStr">
+        <is>
+          <t>Air Canada Flight 143 ran dry after a pounds-versus-kilograms mix-up in the fuel calculation. The plane got less than half the fuel it needed. The pilots glided to an airfield in Gimli, Canada, and landed safely.</t>
+        </is>
+      </c>
+      <c r="F35" s="52" t="inlineStr">
+        <is>
+          <t>Fuel gauge drains; unit labels lb and kg swap; glide path line arcs down to a runway.</t>
+        </is>
+      </c>
+      <c r="G35" s="65">
+        <f>LEN(TRIM(E35))-LEN(SUBSTITUTE(TRIM(E35)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H35" s="58">
+        <f>G35/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="33.75" customHeight="1" s="47">
+      <c r="A36" s="65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" s="65" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C36" s="66" t="inlineStr">
+        <is>
+          <t>Congrats</t>
+        </is>
+      </c>
+      <c r="D36" s="65" t="inlineStr">
+        <is>
+          <t>42-46s</t>
+        </is>
+      </c>
+      <c r="E36" s="52" t="inlineStr">
+        <is>
+          <t>Congrats, you just learned how a jet engine works.</t>
+        </is>
+      </c>
+      <c r="F36" s="52" t="inlineStr">
+        <is>
+          <t>Congrats card: teal check + chime (template).</t>
+        </is>
+      </c>
+      <c r="G36" s="65">
+        <f>LEN(TRIM(E36))-LEN(SUBSTITUTE(TRIM(E36)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H36" s="58">
+        <f>G36/$D$3</f>
+        <v/>
       </c>
     </row>
     <row r="37" ht="33.75" customHeight="1" s="47">
       <c r="A37" s="65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B37" s="65" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C37" s="66" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>CTA</t>
         </is>
       </c>
       <c r="D37" s="65" t="inlineStr">
         <is>
-          <t>0-3s</t>
+          <t>46-49s</t>
         </is>
       </c>
       <c r="E37" s="52" t="inlineStr">
         <is>
-          <t>Myth: planes fly because air pushes up on the wing from below.</t>
+          <t>Follow Unpack and Explain for how things actually work.</t>
         </is>
       </c>
       <c r="F37" s="52" t="inlineStr">
         <is>
-          <t>Wing cross-section with a red 'MYTH' stamp.</t>
+          <t>Logo + tagline card.</t>
         </is>
       </c>
       <c r="G37" s="65">
@@ -3298,207 +3443,382 @@
       </c>
     </row>
     <row r="38" ht="30" customHeight="1" s="47">
-      <c r="A38" s="65" t="inlineStr">
+      <c r="A38" s="67" t="n"/>
+      <c r="B38" s="67" t="n"/>
+      <c r="C38" s="67" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D38" s="67" t="n"/>
+      <c r="E38" s="68">
+        <f>IF(AND(G38&gt;=100,G38&lt;=130),"Within the 100-130 word target","Outside the 100-130 word target")</f>
+        <v/>
+      </c>
+      <c r="F38" s="67" t="n"/>
+      <c r="G38" s="67">
+        <f>SUM(G31:G37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="69">
+        <f>SUM(H31:H37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="33.75" customHeight="1" s="47">
+      <c r="C39" s="70" t="inlineStr">
+        <is>
+          <t>Sources / verify</t>
+        </is>
+      </c>
+      <c r="D39" s="71" t="inlineStr">
+        <is>
+          <t>Verify: altitude, fuel amounts, and that nobody was killed. Source: Canadian investigation report on Air Canada Flight 143. Keep the tone factual and credit the crew's skill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="33.75" customHeight="1" s="47">
+      <c r="C40" s="70" t="inlineStr">
+        <is>
+          <t>Caption + hashtags</t>
+        </is>
+      </c>
+      <c r="D40" s="71" t="inlineStr">
+        <is>
+          <t>Both engines stopped at 41,000 feet and the crew still landed the plane. Here's how a jet engine works, and what went wrong. Save for later.  #aviation #engineering #howitworks #explained</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="33.75" customHeight="1" s="47"/>
+    <row r="42" ht="24" customHeight="1" s="47">
+      <c r="A42" s="64" t="inlineStr">
+        <is>
+          <t>Post 4  |  Q  |  Myth: planes fly because air pushes up from below</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="33.75" customHeight="1" s="47">
+      <c r="A43" s="65" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B38" s="65" t="inlineStr">
+      <c r="B43" s="65" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C38" s="66" t="inlineStr">
+      <c r="C43" s="66" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="D43" s="65" t="inlineStr">
+        <is>
+          <t>0-4s</t>
+        </is>
+      </c>
+      <c r="E43" s="52" t="inlineStr">
+        <is>
+          <t>Do you know what really keeps a plane in the air?</t>
+        </is>
+      </c>
+      <c r="F43" s="52" t="inlineStr">
+        <is>
+          <t>Question card (template).</t>
+        </is>
+      </c>
+      <c r="G43" s="65">
+        <f>LEN(TRIM(E43))-LEN(SUBSTITUTE(TRIM(E43)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H43" s="58">
+        <f>G43/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="33.75" customHeight="1" s="47">
+      <c r="A44" s="65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B44" s="65" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C44" s="66" t="inlineStr">
+        <is>
+          <t>Hook</t>
+        </is>
+      </c>
+      <c r="D44" s="65" t="inlineStr">
+        <is>
+          <t>4-9s</t>
+        </is>
+      </c>
+      <c r="E44" s="52" t="inlineStr">
+        <is>
+          <t>Myth: planes fly because air pushes up on the wing from below.</t>
+        </is>
+      </c>
+      <c r="F44" s="52" t="inlineStr">
+        <is>
+          <t>Wing cross-section with a red 'MYTH' stamp.</t>
+        </is>
+      </c>
+      <c r="G44" s="65">
+        <f>LEN(TRIM(E44))-LEN(SUBSTITUTE(TRIM(E44)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H44" s="58">
+        <f>G44/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="33.75" customHeight="1" s="47">
+      <c r="A45" s="65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B45" s="65" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C45" s="66" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D38" s="65" t="inlineStr">
-        <is>
-          <t>3-8s</t>
-        </is>
-      </c>
-      <c r="E38" s="52" t="inlineStr">
+      <c r="D45" s="65" t="inlineStr">
+        <is>
+          <t>9-12s</t>
+        </is>
+      </c>
+      <c r="E45" s="52" t="inlineStr">
         <is>
           <t>That's only part of the story.</t>
         </is>
       </c>
-      <c r="F38" s="52" t="inlineStr">
+      <c r="F45" s="52" t="inlineStr">
         <is>
           <t>Stamp slides away.</t>
         </is>
       </c>
-      <c r="G38" s="65">
-        <f>LEN(TRIM(E38))-LEN(SUBSTITUTE(TRIM(E38)," ",""))+1</f>
-        <v/>
-      </c>
-      <c r="H38" s="58">
-        <f>G38/$D$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="75.75" customHeight="1" s="47">
-      <c r="A39" s="65" t="inlineStr">
+      <c r="G45" s="65">
+        <f>LEN(TRIM(E45))-LEN(SUBSTITUTE(TRIM(E45)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H45" s="58">
+        <f>G45/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="33.75" customHeight="1" s="47">
+      <c r="A46" s="65" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B39" s="65" t="inlineStr">
+      <c r="B46" s="65" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C39" s="66" t="inlineStr">
+      <c r="C46" s="66" t="inlineStr">
         <is>
           <t>Mechanism</t>
         </is>
       </c>
-      <c r="D39" s="65" t="inlineStr">
-        <is>
-          <t>8-28s</t>
-        </is>
-      </c>
-      <c r="E39" s="52" t="inlineStr">
+      <c r="D46" s="65" t="inlineStr">
+        <is>
+          <t>12-30s</t>
+        </is>
+      </c>
+      <c r="E46" s="52" t="inlineStr">
         <is>
           <t>A wing is tilted and curved, so it bends the air flowing past it downward. Air above the wing speeds up and its pressure drops. Lower pressure on top, higher pressure below, and the wing is pushed up. Push air down, and the air pushes you up.</t>
         </is>
       </c>
-      <c r="F39" s="52" t="inlineStr">
+      <c r="F46" s="52" t="inlineStr">
         <is>
           <t>Streamlines flow around the wing and bend downward; pressure colors (blue on top, orange below); arrow labeled LIFT.</t>
         </is>
       </c>
-      <c r="G39" s="65">
-        <f>LEN(TRIM(E39))-LEN(SUBSTITUTE(TRIM(E39)," ",""))+1</f>
-        <v/>
-      </c>
-      <c r="H39" s="58">
-        <f>G39/$D$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="48" customHeight="1" s="47">
-      <c r="A40" s="65" t="inlineStr">
+      <c r="G46" s="65">
+        <f>LEN(TRIM(E46))-LEN(SUBSTITUTE(TRIM(E46)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H46" s="58">
+        <f>G46/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="33.75" customHeight="1" s="47">
+      <c r="A47" s="65" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B40" s="65" t="inlineStr">
+      <c r="B47" s="65" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C40" s="66" t="inlineStr">
+      <c r="C47" s="66" t="inlineStr">
         <is>
           <t>Payoff</t>
         </is>
       </c>
-      <c r="D40" s="65" t="inlineStr">
-        <is>
-          <t>28-35s</t>
-        </is>
-      </c>
-      <c r="E40" s="52" t="inlineStr">
+      <c r="D47" s="65" t="inlineStr">
+        <is>
+          <t>30-40s</t>
+        </is>
+      </c>
+      <c r="E47" s="52" t="inlineStr">
         <is>
           <t>And no, the air over the top isn't racing to catch up with the air below. It actually gets to the back first.</t>
         </is>
       </c>
-      <c r="F40" s="52" t="inlineStr">
+      <c r="F47" s="52" t="inlineStr">
         <is>
           <t>Two dots race across the wing; the top dot wins.</t>
         </is>
       </c>
-      <c r="G40" s="65">
-        <f>LEN(TRIM(E40))-LEN(SUBSTITUTE(TRIM(E40)," ",""))+1</f>
-        <v/>
-      </c>
-      <c r="H40" s="58">
-        <f>G40/$D$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="33.75" customHeight="1" s="47">
-      <c r="A41" s="65" t="inlineStr">
+      <c r="G47" s="65">
+        <f>LEN(TRIM(E47))-LEN(SUBSTITUTE(TRIM(E47)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H47" s="58">
+        <f>G47/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="33.75" customHeight="1" s="47">
+      <c r="A48" s="65" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B41" s="65" t="inlineStr">
+      <c r="B48" s="65" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C41" s="66" t="inlineStr">
+      <c r="C48" s="66" t="inlineStr">
+        <is>
+          <t>Congrats</t>
+        </is>
+      </c>
+      <c r="D48" s="65" t="inlineStr">
+        <is>
+          <t>40-44s</t>
+        </is>
+      </c>
+      <c r="E48" s="52" t="inlineStr">
+        <is>
+          <t>Congrats, you just learned how a wing really makes lift.</t>
+        </is>
+      </c>
+      <c r="F48" s="52" t="inlineStr">
+        <is>
+          <t>Congrats card: teal check + chime (template).</t>
+        </is>
+      </c>
+      <c r="G48" s="65">
+        <f>LEN(TRIM(E48))-LEN(SUBSTITUTE(TRIM(E48)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H48" s="58">
+        <f>G48/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="33.75" customHeight="1" s="47">
+      <c r="A49" s="65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B49" s="65" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C49" s="66" t="inlineStr">
         <is>
           <t>CTA</t>
         </is>
       </c>
-      <c r="D41" s="65" t="inlineStr">
-        <is>
-          <t>35-38s</t>
-        </is>
-      </c>
-      <c r="E41" s="52" t="inlineStr">
+      <c r="D49" s="65" t="inlineStr">
+        <is>
+          <t>44-47s</t>
+        </is>
+      </c>
+      <c r="E49" s="52" t="inlineStr">
         <is>
           <t>Follow Unpack and Explain for how things actually work.</t>
         </is>
       </c>
-      <c r="F41" s="52" t="inlineStr">
+      <c r="F49" s="52" t="inlineStr">
         <is>
           <t>Logo + tagline card.</t>
         </is>
       </c>
-      <c r="G41" s="65">
-        <f>LEN(TRIM(E41))-LEN(SUBSTITUTE(TRIM(E41)," ",""))+1</f>
-        <v/>
-      </c>
-      <c r="H41" s="58">
-        <f>G41/$D$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="47">
-      <c r="A42" s="67" t="n"/>
-      <c r="B42" s="67" t="n"/>
-      <c r="C42" s="67" t="inlineStr">
+      <c r="G49" s="65">
+        <f>LEN(TRIM(E49))-LEN(SUBSTITUTE(TRIM(E49)," ",""))+1</f>
+        <v/>
+      </c>
+      <c r="H49" s="58">
+        <f>G49/$D$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="67" t="n"/>
+      <c r="B50" s="67" t="n"/>
+      <c r="C50" s="67" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D42" s="67" t="n"/>
-      <c r="E42" s="68">
-        <f>IF(AND(G42&gt;=90,G42&lt;=110),"Within the 90-110 word target","Outside the 90-110 word target")</f>
-        <v/>
-      </c>
-      <c r="F42" s="67" t="n"/>
-      <c r="G42" s="67">
-        <f>SUM(G37:G41)</f>
-        <v/>
-      </c>
-      <c r="H42" s="69">
-        <f>SUM(H37:H41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="33.75" customHeight="1" s="47">
-      <c r="C43" s="70" t="inlineStr">
+      <c r="D50" s="67" t="n"/>
+      <c r="E50" s="68">
+        <f>IF(AND(G50&gt;=100,G50&lt;=130),"Within the 100-130 word target","Outside the 100-130 word target")</f>
+        <v/>
+      </c>
+      <c r="F50" s="67" t="n"/>
+      <c r="G50" s="67">
+        <f>SUM(G43:G49)</f>
+        <v/>
+      </c>
+      <c r="H50" s="69">
+        <f>SUM(H43:H49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="33.75" customHeight="1" s="47">
+      <c r="C51" s="70" t="inlineStr">
         <is>
           <t>Sources / verify</t>
         </is>
       </c>
-      <c r="D43" s="71" t="inlineStr">
+      <c r="D51" s="71" t="inlineStr">
         <is>
           <t>Verify: wording of the lift explanation against NASA Glenn's pages. Keep it simple but not misleading.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="33.75" customHeight="1" s="47">
-      <c r="C44" s="70" t="inlineStr">
+    <row r="52" ht="33.75" customHeight="1" s="47">
+      <c r="C52" s="70" t="inlineStr">
         <is>
           <t>Caption + hashtags</t>
         </is>
       </c>
-      <c r="D44" s="72" t="inlineStr">
+      <c r="D52" s="71" t="inlineStr">
         <is>
           <t>Most of us learned lift wrong. Here's the short version. Save and share with the person who explained it to you.  #aviation #physics #mythbusting #explained</t>
         </is>
@@ -3506,18 +3826,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D40:H40"/>
     <mergeCell ref="A6:H6"/>
-    <mergeCell ref="D44:H44"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3850,7 +4170,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="47">
       <c r="A4" s="50" t="inlineStr">
         <is>
@@ -4016,7 +4335,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="47">
       <c r="A12" s="74" t="inlineStr">
         <is>
